--- a/Benchmark/Meta-Tag/MeSH_OccO_Gold_Standard.xlsx
+++ b/Benchmark/Meta-Tag/MeSH_OccO_Gold_Standard.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
   <si>
     <t xml:space="preserve">MeSH concept</t>
   </si>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Food Quality</t>
   </si>
   <si>
-    <t xml:space="preserve">Food preparation or serving role
+    <t xml:space="preserve">Food preparation or serving role 
 </t>
   </si>
   <si>
@@ -123,7 +123,7 @@
   </si>
   <si>
     <t xml:space="preserve">Food preparation role;
-Management + food preparation role</t>
+Management + food preparation role + Food service skill or ability</t>
   </si>
   <si>
     <t xml:space="preserve">assessed_by, 
@@ -176,6 +176,10 @@
   </si>
   <si>
     <t xml:space="preserve">Nutritive Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food preparation role;
+Management + food preparation role</t>
   </si>
   <si>
     <t xml:space="preserve">checked_by, 
@@ -706,19 +710,19 @@
         <v>32</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>31</v>
@@ -726,7 +730,7 @@
     </row>
     <row r="8" customFormat="false" ht="121.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>22</v>
@@ -735,13 +739,13 @@
         <v>17</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>14</v>
